--- a/data/chinese/P2T3_Chapter17.xlsx
+++ b/data/chinese/P2T3_Chapter17.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE9DD55-2AFD-7042-B565-5FF30E886605}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB53BCC-551B-A740-8926-5B60E98631E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,100 +78,111 @@
     <t>吃驚</t>
   </si>
   <si>
-    <t>感到意外、十分驚訝</t>
-  </si>
-  <si>
     <t>看到他突然出現，大家都非常吃驚。</t>
   </si>
   <si>
     <t>夥伴</t>
   </si>
   <si>
-    <t>一同做事、玩耍的同伴</t>
-  </si>
-  <si>
     <t>我和小夥伴每天放學都一起回家。</t>
   </si>
   <si>
     <t>親切</t>
   </si>
   <si>
-    <t>態度溫和和善，讓人覺得暖心</t>
-  </si>
-  <si>
     <t>爺爺待人十分親切，大家都喜歡他。</t>
   </si>
   <si>
     <t>磨坊</t>
   </si>
   <si>
-    <t>用石磨研磨穀物的廠房</t>
-  </si>
-  <si>
     <t>以前村民都會把麥子送到磨坊磨成麵粉。</t>
   </si>
   <si>
     <t>淹死</t>
   </si>
   <si>
-    <t>沉入水中窒息而亡</t>
-  </si>
-  <si>
     <t>千萬不要獨自靠近深水，避免淹死的危險。</t>
   </si>
   <si>
     <t>蹚過</t>
   </si>
   <si>
+    <t>我們捲起褲腳，蹚過小河到對岸。</t>
+  </si>
+  <si>
+    <t>為難</t>
+  </si>
+  <si>
+    <t>這件事讓他十分為難，遲遲無法決定。</t>
+  </si>
+  <si>
+    <t>擋住</t>
+  </si>
+  <si>
+    <t>樹枝擋住前方的路，我們得繞道走。</t>
+  </si>
+  <si>
+    <t>連蹦帶跳</t>
+  </si>
+  <si>
+    <t>拿到禮物後，妹妹連蹦帶跳地跑回家。</t>
+  </si>
+  <si>
+    <t>怎麼辦</t>
+  </si>
+  <si>
+    <t>鑰匙不見了，我實在不知道怎麼辦。</t>
+  </si>
+  <si>
+    <t>難為情</t>
+  </si>
+  <si>
+    <t>當眾被誇獎，他有點難為情地低下頭。</t>
+  </si>
+  <si>
+    <t>遇到意外的事，感到很驚訝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一起玩、一起做事的同伴、朋友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>態度溫和、讓人感覺很舒服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用來磨米、磨麵的地方，通常有機器或水車</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉進水裡沒法呼吸而失去生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>踩著淺水走過水域</t>
-  </si>
-  <si>
-    <t>我們捲起褲腳，蹚過小河到對岸。</t>
-  </si>
-  <si>
-    <t>為難</t>
-  </si>
-  <si>
-    <t>感到棘手難辦，不知如何處理</t>
-  </si>
-  <si>
-    <t>這件事讓他十分為難，遲遲無法決定。</t>
-  </si>
-  <si>
-    <t>擋住</t>
-  </si>
-  <si>
-    <t>遮攔、阻隔，使無法通過或看見</t>
-  </si>
-  <si>
-    <t>樹枝擋住前方的路，我們得繞道走。</t>
-  </si>
-  <si>
-    <t>連蹦帶跳</t>
-  </si>
-  <si>
-    <t>一邊跳一邊跑，形容開心活潑的樣子</t>
-  </si>
-  <si>
-    <t>拿到禮物後，妹妹連蹦帶跳地跑回家。</t>
-  </si>
-  <si>
-    <t>怎麼辦</t>
-  </si>
-  <si>
-    <t>遇到困境時詢問解決方法</t>
-  </si>
-  <si>
-    <t>鑰匙不見了，我實在不知道怎麼辦。</t>
-  </si>
-  <si>
-    <t>難為情</t>
-  </si>
-  <si>
-    <t>害羞、不好意思，覺得尷尬</t>
-  </si>
-  <si>
-    <t>當眾被誇獎，他有點難為情地低下頭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>覺得很難辦、不知道怎麼做才好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用東西遮住、攔住，不讓通過</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一邊跳一邊走，形容很開心、很活潑的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遇到困難時，不知道該怎麼解決，心裡著急的樣子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>因為害羞、不好意思而臉紅、尷尬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -915,10 +926,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -927,13 +938,13 @@
     </row>
     <row r="5" spans="1:11" ht="27">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -942,13 +953,13 @@
     </row>
     <row r="6" spans="1:11" ht="27">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3">
         <v>2</v>
@@ -957,13 +968,13 @@
     </row>
     <row r="7" spans="1:11" ht="27">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -972,13 +983,13 @@
     </row>
     <row r="8" spans="1:11" ht="27">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -987,13 +998,13 @@
     </row>
     <row r="9" spans="1:11" ht="27">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1002,13 +1013,13 @@
     </row>
     <row r="10" spans="1:11" ht="27">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3">
         <v>3</v>
@@ -1017,13 +1028,13 @@
     </row>
     <row r="11" spans="1:11" ht="27">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -1032,13 +1043,13 @@
     </row>
     <row r="12" spans="1:11" ht="27">
       <c r="A12" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -1047,13 +1058,13 @@
     </row>
     <row r="13" spans="1:11" ht="27">
       <c r="A13" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3">
         <v>3</v>
@@ -1062,13 +1073,13 @@
     </row>
     <row r="14" spans="1:11" ht="27">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3">
         <v>3</v>
